--- a/paper/source_data/ed_table1_source_data.xlsx
+++ b/paper/source_data/ed_table1_source_data.xlsx
@@ -457,7 +457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256.</t>
+          <t>One sheet per panel with exactly the plotted values, intervals, floored counts and labels. Each row names the aggregate file it was read from and that file's SHA-256, with one further column pair for each further file a row was read from.</t>
         </is>
       </c>
     </row>
